--- a/docs/brand-color-impact.xlsx
+++ b/docs/brand-color-impact.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -978,22 +978,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>主色 / 价值色</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>价值色(珊瑚)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ 建议固定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>btn-amber</t>
+          <t>.btn btn-amber 硬编码渐变 #FF9879→#F2563B</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>--org-primary（按钮主色随品牌）</t>
+          <t>价值色体系，与会员价值色一致；若随品牌色会出现「品牌色按钮 + 珊瑚角标」双主色打架；Chat.tsx:568/572</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>硬编码渐变 #7179F8→#3C49D6</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary；.btn-primary 从不引用 --indigo，须先收敛硬编码；styles.css:179-180</t>
         </is>
       </c>
     </row>
@@ -1323,37 +1323,37 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>登录页</t>
+          <t>KP 判活入口页(新增)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>登录按钮</t>
+          <t>下架/失效提示图标底+图标</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>语义琥珀/珊瑚</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>amber-soft / terra-soft</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>拦截页语义色固定；screens/KpGate.tsx:72-81</t>
         </is>
       </c>
     </row>
@@ -1363,37 +1363,37 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>登录页</t>
+          <t>我的纸书</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>左侧品牌区 blob / 知识核</t>
+          <t>整卡降透明(已下架/已失效)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>主→辅渐变</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>中性降透明</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>硬编码</t>
+          <t>.bk-dim opacity .55</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>--org-grad</t>
+          <t>不着色，只降透明；mobile-app.css:1363</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>全局·侧栏</t>
+          <t>我的纸书</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>菜单激活态(左竖条+底色+文字)</t>
+          <t>「已解锁」封面角标</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>语义成功绿</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>--side-active / --indigo</t>
+          <t>.bk-tag-unlock var(--jade)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>mobile-app.css:1367</t>
         </is>
       </c>
     </row>
@@ -1443,37 +1443,37 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>我的纸书</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>主操作按钮(新建/保存/导出)</t>
+          <t>「已下架/已失效」中性胶囊</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>主色填充</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>中性灰</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>.bk-st rgba(23,26,33,.055)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>mobile-app.css:1369，0718 已去彩色</t>
         </is>
       </c>
     </row>
@@ -1483,37 +1483,37 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>我的永享</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Tab 选中下划线</t>
+          <t>「已失效」珊瑚标 / 「已下架」琥珀标</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>语义色</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>.yx-dead / .yx-off</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>mobile-app.css:1377/1379</t>
         </is>
       </c>
     </row>
@@ -1523,37 +1523,37 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>我的永享</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>链接 / 可点文字</t>
+          <t>失效封面置灰</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>灰度滤镜</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>.yx-cover.dead grayscale(1)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>mobile-app.css:1376</t>
         </is>
       </c>
     </row>
@@ -1563,22 +1563,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>开通会员(双模式)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>开关 / 单选 / 复选 选中态</t>
+          <t>权益速览 chip</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
+          <t>主色字 + 主色淡描边</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>var(--indigo-ink) + rgba(75,87,232,.14)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary；mobile-app.css:1384</t>
         </is>
       </c>
     </row>
@@ -1603,37 +1603,37 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>开通会员(双模式)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>输入框聚焦边框</t>
+          <t>套餐卡选中态(描边+底+对勾)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>价值橙</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ 建议固定</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>.mb-plan.sel var(--amber)</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>会员体系统一橙；mobile-app.css:1389/1393</t>
         </is>
       </c>
     </row>
@@ -1643,37 +1643,37 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>开通会员(双模式)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>进度条 / 配额条填充</t>
+          <t>「首月特惠」角标</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>珊瑚渐变</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ 建议固定</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>--indigo</t>
+          <t>.mb-plan-badge 硬编码 #FF9879→#F2563B</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>mobile-app.css:1390</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1683,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>主控台</t>
+          <t>我的订单 / 订单详情</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>趋势图 / KPI 图表主色系</t>
+          <t>退款处理中状态字</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>主色系</t>
+          <t>主色</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Recharts 硬编码</t>
+          <t>.refund-state.processing var(--indigo)</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary；mobile-app.css:1343</t>
         </is>
       </c>
     </row>
@@ -1723,22 +1723,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>主控台</t>
+          <t>微信扫码登录</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>当前订阅卡强调 / 徽标</t>
+          <t>扫码状态圆形图标</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>主色</t>
+          <t>主色淡底 + 主色</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>硬编码</t>
+          <t>.wxscan-mask-ic</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary/-soft；mobile-app.css:1303-1308</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1763,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>数据看板</t>
+          <t>微信扫码登录</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>留存/来源/分布等图表主色系</t>
+          <t>「返回」文字链</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>主色系</t>
+          <t>主色深阶</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Recharts 硬编码</t>
+          <t>.wxscan-back var(--indigo-ink)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary；mobile-app.css:1330-1332</t>
         </is>
       </c>
     </row>
@@ -1803,22 +1803,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>机构后台 PC</t>
+          <t>机构前台 H5</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>数据看板</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>提问关键词云·色深</t>
+          <t>答案反馈标签选中态</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>主色系</t>
+          <t>主色淡底 + 主色字</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>硬编码</t>
+          <t>.fbk-tag.on</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>--org-primary</t>
+          <t>--org-primary/-soft；mobile-app.css:672-675</t>
         </is>
       </c>
     </row>
@@ -1843,37 +1843,37 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>三端通用</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>登录页</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>成功 / 已解锁 / 上架 标识</t>
+          <t>登录按钮</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>语义成功绿</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>--jade</t>
+          <t>--indigo</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>语义色固定——变了会失去「成功」直觉</t>
+          <t>--org-primary</t>
         </is>
       </c>
     </row>
@@ -1883,37 +1883,37 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>三端通用</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>登录页</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>删除 / 危险 / 错误 / 退款</t>
+          <t>左侧品牌区 blob / 知识核</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>语义错误红</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主→辅渐变</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>--terra</t>
+          <t>硬编码</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>语义色固定——警示性不能被品牌色稀释</t>
+          <t>--org-grad</t>
         </is>
       </c>
     </row>
@@ -1923,37 +1923,37 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>机构前台 H5</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>登录 / 支付</t>
+          <t>全局·侧栏</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>微信登录 · 微信支付 按钮</t>
+          <t>菜单激活态(左竖条+底色+文字)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>微信品牌绿</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>微信绿</t>
+          <t>--side-active / --indigo</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>微信官方品牌色，识别度与合规要求，不可改</t>
+          <t>--org-primary</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>三端通用</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1973,27 +1973,27 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>正文 / 标题 文字</t>
+          <t>主操作按钮(新建/保存/导出)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>中性墨色</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色填充</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>--ink / --ink-2</t>
+          <t>硬编码渐变 #7179F8→#3C49D6</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>中性色，保证可读性，品牌色只做点缀不做正文</t>
+          <t>--org-primary；.btn-primary 从不引用 --indigo，hover 另有硬编码 #413bab；styles.css:179-180</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>三端通用</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2013,27 +2013,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>页面 / 卡片 背景</t>
+          <t>Tab 选中下划线</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>奶白 / 白</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>--surface / --paper</t>
+          <t>--indigo</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>中性底；品牌色仅用于强调，不做大面积背景</t>
+          <t>--org-primary</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>三端通用</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2053,27 +2053,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>边框 / 分隔线</t>
+          <t>链接 / 可点文字</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>中性灰</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>--line / --line-2</t>
+          <t>--indigo</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>中性结构色，跨机构统一</t>
+          <t>--org-primary</t>
         </is>
       </c>
     </row>
@@ -2083,37 +2083,37 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>机构前台 H5</t>
+          <t>机构后台 PC</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>AI 会话</t>
+          <t>全局</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>资源类型角标(图 / 音 / 视)</t>
+          <t>开关 / 单选 / 复选 选中态</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>类型区分色</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>❌ 不需变</t>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>--indigo</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>类型标识跨机构一致，便于用户快速识别</t>
+          <t>--org-primary</t>
         </is>
       </c>
     </row>
@@ -2123,35 +2123,2195 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>输入框聚焦边框</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>--indigo</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>上传 / 反馈处理进度条填充</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>--indigo</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary（.up-item-bar i / .fbar i）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>配额用量进度条填充</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>语义三色(绿/橙/红)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>.quota-fill ok/warn/bad = jade/amber/terra</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>用量健康度语义，不能被品牌色吃掉；admin-app.css:1815-1817</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>趋势图 / KPI 图表主色系</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>主色系</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Recharts 硬编码</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>当前订阅卡强调 / 徽标</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>硬编码</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>留存/来源/分布等图表主色系</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>主色系</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Recharts 硬编码</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>提问关键词云·色深</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>主色系</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>硬编码</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>KPI 卡 hover 顶条 + 右上角光晕</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>主渐变 / 主色半透</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>var(--grad) + rgba(75,87,232,.09)</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；admin-app.css:2301-2320</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>段标题左侧渐变竖条</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>主渐变</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>var(--grad)</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；admin-app.css:2360-2368</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>主题 Tab 选中字 + 渐变指示条 + hover 底</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>主色深阶 / 主渐变</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo-ink) / var(--grad)</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-grad；admin-app.css:2374-2376</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>数据看板·留存三卡</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>留存率大数字(渐变文字)</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>主→辅渐变文字</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #3d6ff5→#8b6cf6</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；admin-app.css:2380-2387</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>数据看板·留存三卡</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>留存比例条 轨道 + 填充</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主渐变</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo-soft) + 硬编码渐变</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary-soft/--org-grad；admin-app.css:2389-2399</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>数据看板·留存三卡</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>「待成熟」占位卡</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>中性虚线灰</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>.ret-pending 中性</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>占位态不着色；admin-app.css:2401-2418</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>数据看板·来源分布</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>环形图弧段 + 投影</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>主→辅渐变</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #3D6FF5→#8B6CF6</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；DataBoard.tsx:294-301</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>数据看板·来源分布</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>图例色块 + 行 hover 底</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>主→辅渐变 / 主色淡底</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>硬编码渐变 / var(--indigo-soft)</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad/-soft；DataBoard.tsx:310</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>新增用户/提问量迷你趋势折线</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>主色系</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #4B57E8</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；DataBoard.tsx:283/369</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>全局·图表</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>折线图 hover 竖向指引线</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #4B57E8</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；ui-admin/LineChart.tsx:55（三端共用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>「按注册时间」标签</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色字</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>.tag-indigo</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；styles.css:196</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>区间分析条 / 排行行 hover</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo-soft)</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary-soft；admin-app.css:2152/2194</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>订阅方案行选中态(描边+底+对勾)</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>主色 + 主色淡底</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>.sub-plan-row.on / .spr-check</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:552-586</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>额度卡 hover/focus 态 + 图标圆底</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>主色描边 + 主色淡底</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>.quota-card / .qc-ic</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:596-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>额度步进器 +/− hover、输入聚焦环</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>主色描边 + 主色半透光环</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>.qty-stepper var(--indigo) + rgba(75,87,232,.14)</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；admin-app.css:608/612</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>说明条圆点 / 规则列表项目符</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>.quota-note::before / .sub-tip-rules li::before</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；admin-app.css:618/671</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>订阅与配额</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>「占用量」额度类型标</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色字</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>.quota-kind.occupancy</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:2263（消耗量用 amber 不变）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>加油包抽屉</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>空态插画</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>主色描边+填充</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #4B57E8 多处</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；ui-admin/SubPackDrawer.tsx:49-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Agent 列表 / 详情</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>「机构」类型标</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色字</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>.tag-indigo（0718 从绿改靛）</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；AgentList.tsx:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Agent 列表</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Agent 头像渐变底</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>主→辅渐变</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #7c8bf5→#5562d8</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；AgentList.tsx:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>C 端用户详情</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>用户头像光球</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>主→辅渐变</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #7c8bf5→#4b57e8</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；CUserDetail.tsx:69</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>知识 KP 详情</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>内容 Tab 选中下划线</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>.kpd-tab.on::after var(--indigo)</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；proto-admin.css:247</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>知识 KP 列表 / 详情</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>发布状态标(已发布/已下架/草稿)</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>语义绿/琥珀/灰描边</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>tag-jade / tag-amber / tag-line</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>0718 已把「已发布」从电光靛改语义绿，勿再回收品牌色；proto-admin.css:506-511</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>全局·表单</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>禁用置灰统一标准</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>中性纸白底 + 中性边</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>.inp2.disabled / .sel-disabled</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>禁用态必须中性，品牌色会被误读成可用；proto-admin.css:436-440</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>全局·下拉</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>选项选中态 / 禁用项</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底+主色字 / 中性</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变 · 禁用项不变</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>.dd-opt.on / .dd-opt.disabled</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:68-70/989</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>前台访问地址输入框聚焦态</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>主色描边 + 主色半透光环</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>.domain-input:focus-within</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；admin-app.css:2251</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>全局·上传</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>拖拽区 hover/激活态</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>主色描边+淡底+字</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>.up-drop</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:1892-1896</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>答案反馈工作台</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>用户气泡渐变底</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>主渐变</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>var(--grad-bubble)</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>--org-grad；proto-admin.css:148</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>答案反馈工作台</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>处理中状态 + 进度条</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>.fstat.ing / .fbar i</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；proto-admin.css:255/262</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>账号与权限</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>角色列表选中态</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色字</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>.role.on</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；proto-admin.css:308/405</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>账号与权限</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>权限嵌套子项连接线</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>中性灰虚线</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>.perm-child-wrap::before dashed var(--ink-3)</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>已刻意去掉子项紫色底、只留缩进+虚线；proto-admin.css:423-427</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>账号与权限</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>读/写权限档位块</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>.lvl-seg b.on.write</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；proto-admin.css:88/100</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>全局·时间筛选</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>分段控件选中 / 日历选中日 / 区间内</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>主色 + 主色淡底</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>.seg b.on / .cal-d.sel / .cal-d.inrange</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；proto-admin.css:208/451-467</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>全局·时间筛选</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>自定义区间回显 chip</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色字</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>.dr-applied</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:996-1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>全局·表格</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>排序箭头激活态</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>.tbl th.sortable.asc/.desc .sort i</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；proto-admin.css:392-393</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>全局·顶栏</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>用户菜单 hover / 头像 / 空态插画</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色深阶</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>.menu-row:hover / .pc-avatar / .eill</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary/-soft；admin-app.css:174-281</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>头像裁剪缩放滑块 / 密码强度提示</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>.acrop-zoom accent-color / .cred-pwd</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；admin-app.css:429/708</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>知识 KP 详情·媒体</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>播放键/进度条/倍速/波形激活</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>主色</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>.mv-pp / .mv-track i / .mv-bars span.on</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；admin-app.css:1417-1532</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>导出(两后台通用)</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>导出 xlsx 表头填充 / 标题栏底</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>主色深阶实底 + 白字</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 argb FF3730A3 / FFF2F4FF</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；ui-admin/exportCsv.ts:87/120——导出件是带出机构的交付物，最该跟品牌走</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>所有主色 / 渐变元素</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>平台自身品牌</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>固定 --indigo / --grad</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>超管是平台侧界面、不属于任何机构，必须固定平台色；19 个视图与机构后台共用 proto-admin.css + admin-app.css，换变量时勿误伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
           <t>三端通用</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>成功 / 已解锁 / 上架 标识</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>语义成功绿</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>--jade</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>语义色固定——变了会失去「成功」直觉</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>三端通用</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>删除 / 危险 / 错误 / 退款</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>语义错误红</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>--terra</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>语义色固定——警示性不能被品牌色稀释</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>登录 / 支付</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>微信登录 · 微信支付 按钮</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>微信品牌绿</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>微信绿</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>微信官方品牌色，识别度与合规要求，不可改</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>三端通用</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>正文 / 标题 文字</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>中性墨色</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>--ink / --ink-2</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>中性色，保证可读性，品牌色只做点缀不做正文</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>三端通用</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>页面 / 卡片 背景</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>奶白 / 白</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>--surface / --paper</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>中性底；品牌色仅用于强调，不做大面积背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>三端通用</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>边框 / 分隔线</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>中性灰</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>--line / --line-2</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>中性结构色，跨机构统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>资源类型角标(图 / 音 / 视)</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>类型区分色</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>固定</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>类型标识跨机构一致，便于用户快速识别</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>三端通用</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>会员体系</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>会员标识 / 会员价值色</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>价值橙</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>⚠️ 建议固定</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>--amber</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>会员是平台级权益体系，建议跨机构统一色（可商议）</t>
         </is>

--- a/docs/brand-color-impact.xlsx
+++ b/docs/brand-color-impact.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4317,6 +4317,206 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>我的订单 / 订单详情（0724 新增）</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>待支付条（剩余支付时间倒计时）</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>警示琥珀淡底 + 琥珀字</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>var(--amber-soft) + var(--amber-ink)</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>支付时限警示语义色固定；mobile-app.css:1408</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>我的订单 / 订单详情（0724 新增）</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>「去支付」按钮</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>主色填充</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo)</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；mobile-app.css:1410</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>登录 / 绑定 / 换绑 验证码（0724 新增）</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>语音验证码入口「接听语音电话获取」文字链</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>主色文字链</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary；mobile-app.css:1414</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>登录 / 绑定 / 换绑 验证码（0724 新增）</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>语音拨打中状态行（淡底 + 号段强调 + 重拨按钮）</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>主色淡底 + 主色深字 + 主色按钮</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>✅ 需变</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>var(--indigo-soft) / var(--indigo-ink) / var(--indigo)</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>--org-primary 三阶（color-mix 生成 soft / base / ink）；mobile-app.css:1415-1423</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板（0724 新增）</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>商业化 / LLM 消耗卡图标色条（tone-amber / tone-jade）</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>分类语义色渐变</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>硬编码 #ff8a6b→#ff6f55 / #2fd3a0→#15b080</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>平台超管端整端固定平台色、不参与机构换肤；admin-app.css:2543/2547</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/brand-color-impact.xlsx
+++ b/docs/brand-color-impact.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00DC2626"/>
     </font>
   </fonts>
   <fills count="5">
@@ -80,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,6 +98,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -462,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -573,27 +582,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>知识核动效球</t>
+          <t>产品 logo（0807-4 替换知识核球，周边彩带环动画已按反馈移除）</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>主→辅渐变</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
+          <t>产品 logo 固定色</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>硬编码</t>
+          <t>BRAND_LOGO(base64 png)，styles.css .core-logo</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>--org-grad</t>
+          <t>产品 logo 不随机构换肤</t>
         </is>
       </c>
     </row>
@@ -601,39 +610,39 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>机构前台 H5</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>登录落地页</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>「问书」渐变标题</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>登录落地页（0807 删除）</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>「问书」网页字体渐变标题——已删除，由 logo 文字标题图替代（见文末 0807 新增行）</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>主→辅渐变文字</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>--grad</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>--org-grad</t>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>❌ 已删除</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>原 --grad（login-wm2），元素已移除</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>0807：网页字体渐变标题随真实 LOGO 接入移除，不再存在换肤点</t>
         </is>
       </c>
     </row>
@@ -1881,39 +1890,39 @@
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>机构后台 PC</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>登录页</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>左侧品牌区 blob / 知识核</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>主→辅渐变</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需变</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>硬编码</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>--org-grad</t>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>两后台 PC</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>登录页（0807 明确两后台共用）</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>品牌区横版 logo（图标＋文字，0807-4 替换知识核球并移除「AI 问书」文字标题与彩带环）</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 固定色（blob 背景保留可随）</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>⚠️ 建议固定</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>BRAND_LOGO_FULL + login-blob；proto-admin.css .login-logo-full</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 不随机构换肤，背景 blob 可随机构色；机构后台与平台超管登录页同资产同样式</t>
         </is>
       </c>
     </row>
@@ -4514,6 +4523,646 @@
       <c r="H101" s="3" t="inlineStr">
         <is>
           <t>平台超管端整端固定平台色、不参与机构换肤；admin-app.css:2543/2547</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>两后台 PC</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>C 端用户 / 全域用户 / 答案反馈（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>会员状态四态标（有效会员 / 宽限期（待续费）/ 会员已过期 / 未开通会员）</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>生命周期语义四色（玉绿 / 琥珀 / 赤陶 / 灰描边）</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>.tag-jade / .tag-amber / .tag-terra / .tag-line 全复用</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>状态健康度语义色固定、零新增 CSS；映射单一来源 packages/mock/src/data/memberState.ts:19-24；styles.css:196-199</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>我的 / 会话抽屉（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>会员标四态变体「会员 · 待续费」</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>价值橙（同原会员标）</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>⚠️ 建议固定</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>var(--amber-soft) + var(--amber-ink)（.tag-s.tag-amber）</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>沿用会员价值色跨机构统一建议（同上「会员标识」条）；My.tsx / Chat.tsx 渲染</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>两后台 PC</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Agent 详情（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>TTS 参考音文本输入框（聚焦态）</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>主色描边</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>var(--indigo)</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>后台表单聚焦态统一平台色；proto-admin.css:289</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>两后台 PC</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Agent 详情（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>TTS 参考音文本实时字数（右下角，满 100 字转警示）</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>中性灰 → 危险赤陶</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>var(--ink-3) → var(--terra)（.full）</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>上限警示语义色固定；proto-admin.css:290-291</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>顶栏（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>机构类型演示切换（父机构 / 子机构 / 独立机构，选中态）</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>主色实底 + 白字；容器虚线边暖底</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>var(--indigo) 选中 / var(--surface-warm) + 虚线 var(--line-2)</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>〔演示〕控件非上线功能，虚线边刻意与正式控件区分；admin-app.css:2612-2616</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>六业务页筛选区（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>「机构」单选下拉的「父机构」标</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>靛蓝浅底标</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>.tag-s.tag-indigo（Dropdown 内建 PARENT_SUFFIX 渲染）</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>与平台后台机构下拉父机构标同源同色；Dropdown.tsx:33-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>主控台 / 数据看板（0807 新增，0807-2 视觉重做）</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>「机构」多选下拉——自绘勾选框（选中态）+ 父机构标 + 回填省略</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>主色实底勾选框 + 靛蓝标</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>var(--indigo)（.ms-box.on）+ .tag-s.tag-indigo</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>与单选 Dropdown 同视觉体系；admin-app.css .ms-box/.ms-display/.ms-divider 段</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>主控台（0807-2 新增）</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>订阅卡右上角「本机构订阅」注明胶囊</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>中性灰暖底描边</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>var(--surface-warm)+var(--line)+var(--ink-3)（.sub-scope-note）</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>合同信息与数据筛选解耦的辅助说明；admin-app.css .sub-scope-note</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>主控台（0807-2 新增）</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>实时总览第二行内容供给三卡（KPI 副行分布明细）</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>中性灰副行 + 三色图标章</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>var(--ink-3)（.kpi-sub）+ indigo/jade/amber-soft 图标底</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>平台端固定平台色；admin-app.css .kpi-sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>微信授权弹窗（0807-4）</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>app 头像（蓝底 app 图标版，按反馈定稿）</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 固定色</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>BRAND_LOGO_APP + .wxauth-logo-app</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>仿微信真实授权样式；mobile-app.css .wxauth-logo-app</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>两后台 PC</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>侧栏品牌位（0807-4，0807 明确两后台共用）</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>横版 logo（图标＋文字，替换原光球与「AI 问书」文字；折叠态切纯图标）</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 固定色</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>BRAND_LOGO_FULL / BRAND_LOGO（.side-logo-full / .side-logo-icon）</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>两后台共用 AdminShell；产品 logo 不随机构换肤</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>KP / Agent 卡片（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>数据归属机构行 +「仅可查看」描边标（父机构视角）</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>中性灰 + 灰描边</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>var(--ink-3) + var(--line)（.kp-org-row / .kp-org-ro）</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>辅助信息中性色、不与状态标抢视觉；admin-app.css:2620-2621</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>机构后台 PC</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>KP / Agent 详情（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>子机构数据只读横幅</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>锁定提示灰</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>.kp-readonly-banner 复用（0716 实时分享只读横幅）</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>同一只读语义复用同一样式，零新增；KpDetailView readonlyBanner / AgentDetailView readonlyBanner</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 机构资料（0807 新增，0807-2 更名去 PPT）</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>批量上传弹窗（拖拽框 / 进度条 / 文件列表）</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>复用 KP 知识库上传弹窗全套</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>.up-drop / .up-item-bar 等复用（UploadModal 共享组件）</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>组件抽取自 KP 知识库、样式零新增；admin-app.css:1868-2045</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>主控台（0807 修订）</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>「机构」筛选单选升级多选——自绘勾选框（选中态）＋父机构标＋回填省略；原父机构汇总说明行（靛蓝底引用块）已删除</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>主色实底勾选框 + 靛蓝标</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>var(--indigo)（.ms-box.on）+ .tag-s.tag-indigo（复用机构后台 MultiSelect 共享组件）</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>平台端固定平台色；与机构后台主控台多选同组件同视觉</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>机构前台 H5</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>登录落地页（0807 新增）</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>logo 文字标题图（纯图标下方，替换原网页字体渐变标题）</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 固定色</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>BRAND_LOGO_TEXT，styles.css .landing-logo-text</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>产品 logo 不随机构换肤</t>
         </is>
       </c>
     </row>

--- a/docs/brand-color-impact.xlsx
+++ b/docs/brand-color-impact.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5097,17 +5097,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>主控台（0807 修订）</t>
+          <t>机构详情 · 微信配置（0807-2 修订）</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>「机构」筛选单选升级多选——自绘勾选框（选中态）＋父机构标＋回填省略；原父机构汇总说明行（靛蓝底引用块）已删除</t>
+          <t>敏感项「已配置/已上传」状态行（玉绿状态字 + 等宽尾号/文件名 + 灰更新时间 + 靛蓝操作链接）；原显隐眼睛删除</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>主色实底勾选框 + 靛蓝标</t>
+          <t>语义绿 + 中性灰 + 主色链接</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>var(--indigo)（.ms-box.on）+ .tag-s.tag-indigo（复用机构后台 MultiSelect 共享组件）</t>
+          <t>var(--jade)/var(--ink)/var(--ink-3)/var(--indigo)（.sec-state/.sec-op，admin-app.css）</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>平台端固定平台色；与机构后台主控台多选同组件同视觉</t>
+          <t>平台端固定平台色；状态行沿用只读框标准（纸白底+浅边），零新增色值</t>
         </is>
       </c>
     </row>
@@ -5132,35 +5132,75 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
+          <t>平台超管 PC</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>主控台（0807 修订）</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>「机构」筛选单选升级多选——自绘勾选框（选中态）＋父机构标＋回填省略；原父机构汇总说明行（靛蓝底引用块）已删除</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>主色实底勾选框 + 靛蓝标</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>❌ 不需变</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>var(--indigo)（.ms-box.on）+ .tag-s.tag-indigo（复用机构后台 MultiSelect 共享组件）</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>平台端固定平台色；与机构后台主控台多选同组件同视觉</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
           <t>机构前台 H5</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>登录落地页（0807 新增）</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>logo 文字标题图（纯图标下方，替换原网页字体渐变标题）</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>产品 logo 固定色</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>❌ 不需变</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
+      <c r="G118" s="6" t="inlineStr">
         <is>
           <t>BRAND_LOGO_TEXT，styles.css .landing-logo-text</t>
         </is>
       </c>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>产品 logo 不随机构换肤</t>
         </is>

--- a/docs/brand-color-impact.xlsx
+++ b/docs/brand-color-impact.xlsx
@@ -5097,17 +5097,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>机构详情 · 微信配置（0807-2 修订）</t>
+          <t>机构详情 · 微信配置（0810 修订）</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>敏感项「已配置/已上传」状态行（玉绿状态字 + 等宽尾号/文件名 + 灰更新时间 + 靛蓝操作链接）；原显隐眼睛删除</t>
+          <t>敏感项「已配置/已上传」状态行（玉绿状态字 + 靛蓝操作链接）；0810 起状态行只保留「状态 + 操作」两段——等宽尾号/文件名与灰色更新时间不再展示（原 0807-2 展示取消），显隐眼睛此前已删除</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>语义绿 + 中性灰 + 主色链接</t>
+          <t>语义绿 + 主色链接</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>var(--jade)/var(--ink)/var(--ink-3)/var(--indigo)（.sec-state/.sec-op，admin-app.css）</t>
+          <t>var(--jade)/var(--indigo)（.sec-state/.sec-op，admin-app.css；.sec-tail/.sec-at 两个中性灰样式类随之删除，容器改 inline-flex 随内容收窄）</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
